--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_magallanes_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_magallanes_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:12</t>
+    <t xml:space="preserve">2026-09-29 14:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_magallanes_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_magallanes_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:09</t>
+    <t xml:space="preserve">2026-09-29 18:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,7 +493,7 @@
         <v>11.87</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>57.37</v>
+        <v>57.38</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>45.5</v>
@@ -535,10 +535,10 @@
         <v>-108.76</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>114.04</v>
+        <v>114.05</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>222.81</v>
+        <v>222.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_magallanes_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_magallanes_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:39</t>
+    <t xml:space="preserve">2026-10-05 04:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -496,7 +496,7 @@
         <v>57.38</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>45.5</v>
+        <v>45.51</v>
       </c>
     </row>
     <row r="3">
@@ -538,7 +538,7 @@
         <v>114.05</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>222.8</v>
+        <v>222.81</v>
       </c>
     </row>
   </sheetData>
